--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <r>
       <rPr>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>启用状态</t>
+  </si>
+  <si>
+    <t>平台备注</t>
   </si>
 </sst>
 </file>
@@ -1488,31 +1491,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="14.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="11.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="12.6363636363636" customWidth="1"/>
-    <col min="5" max="6" width="10.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="9.63636363636364" customWidth="1"/>
-    <col min="8" max="8" width="14.8181818181818" customWidth="1"/>
-    <col min="9" max="9" width="14.3636363636364" customWidth="1"/>
-    <col min="10" max="11" width="14.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="12.8181818181818" customWidth="1"/>
-    <col min="13" max="13" width="11.6363636363636" customWidth="1"/>
-    <col min="14" max="14" width="14.4545454545455" customWidth="1"/>
-    <col min="15" max="15" width="12.4545454545455" customWidth="1"/>
-    <col min="16" max="16" width="11.7272727272727" customWidth="1"/>
-    <col min="17" max="18" width="11.9090909090909" customWidth="1"/>
-    <col min="19" max="19" width="11.6363636363636" customWidth="1"/>
-    <col min="22" max="22" width="22.0909090909091" customWidth="1"/>
-    <col min="23" max="23" width="13.5454545454545" customWidth="1"/>
-    <col min="24" max="24" width="15.8181818181818" customWidth="1"/>
-    <col min="25" max="25" width="10.7272727272727" customWidth="1"/>
-    <col min="26" max="26" width="13.0909090909091" customWidth="1"/>
-    <col min="27" max="27" width="14.3636363636364" customWidth="1"/>
-    <col min="28" max="28" width="18.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="12.275" customWidth="1"/>
+    <col min="2" max="2" width="14.4583333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.9083333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.6333333333333" customWidth="1"/>
+    <col min="5" max="6" width="10.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="9.63333333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.8166666666667" customWidth="1"/>
+    <col min="9" max="9" width="14.3666666666667" customWidth="1"/>
+    <col min="10" max="11" width="14.6333333333333" customWidth="1"/>
+    <col min="12" max="12" width="12.8166666666667" customWidth="1"/>
+    <col min="13" max="13" width="11.6333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.4583333333333" customWidth="1"/>
+    <col min="15" max="15" width="12.4583333333333" customWidth="1"/>
+    <col min="16" max="16" width="11.725" customWidth="1"/>
+    <col min="17" max="18" width="11.9083333333333" customWidth="1"/>
+    <col min="19" max="19" width="11.6333333333333" customWidth="1"/>
+    <col min="22" max="22" width="22.0916666666667" customWidth="1"/>
+    <col min="23" max="23" width="13.5416666666667" customWidth="1"/>
+    <col min="24" max="24" width="15.8166666666667" customWidth="1"/>
+    <col min="25" max="25" width="10.725" customWidth="1"/>
+    <col min="26" max="26" width="13.0916666666667" customWidth="1"/>
+    <col min="27" max="27" width="14.3666666666667" customWidth="1"/>
+    <col min="28" max="28" width="18.5416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -1598,7 +1601,7 @@
         <v>23</v>
       </c>
       <c r="AB1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -101,17 +101,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <r>
+      <t>*</t>
     </r>
     <r>
       <rPr>
@@ -135,13 +128,30 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>国家</t>
+    </r>
+  </si>
+  <si>
+    <t>语言</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -152,27 +162,47 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 国家</t>
-    </r>
-  </si>
-  <si>
-    <t>语言</t>
-  </si>
-  <si>
-    <t>邮箱</t>
-  </si>
-  <si>
-    <t>电话</t>
-  </si>
-  <si>
+      <t>负责人</t>
+    </r>
+  </si>
+  <si>
+    <t>负责部门</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>合作平台</t>
+    </r>
+  </si>
+  <si>
+    <t>账号ID</t>
+  </si>
+  <si>
+    <t>账号名称</t>
+  </si>
+  <si>
+    <t>粉丝数量</t>
+  </si>
+  <si>
+    <t>主页链接</t>
+  </si>
+  <si>
+    <t>平台备注</t>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -183,24 +213,32 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 负责人</t>
-    </r>
-  </si>
-  <si>
-    <t>负责部门</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
+      <t>地址信息国家</t>
+    </r>
+  </si>
+  <si>
+    <t>省/州</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>城市</t>
+    </r>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -211,114 +249,40 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 合作平台</t>
-    </r>
-  </si>
-  <si>
-    <t>账号ID</t>
-  </si>
-  <si>
-    <t>账号名称</t>
-  </si>
-  <si>
-    <t>粉丝数量</t>
-  </si>
-  <si>
-    <t>主页链接</t>
-  </si>
-  <si>
-    <t>省/州</t>
-  </si>
-  <si>
+      <t>详细地址</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>联系人</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 城市</t>
-    </r>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 详细地址</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 联系人</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 电话</t>
-    </r>
+      <t>联系人电话</t>
+    </r>
+  </si>
+  <si>
+    <t>联系人邮编</t>
   </si>
   <si>
     <t>默认地址</t>
@@ -327,7 +291,7 @@
     <t>启用状态</t>
   </si>
   <si>
-    <t>平台备注</t>
+    <t>地址备注</t>
   </si>
 </sst>
 </file>
@@ -340,7 +304,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,6 +461,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1568,40 +1538,40 @@
         <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -104,6 +104,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -128,6 +135,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -152,6 +166,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -173,6 +194,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -196,7 +224,19 @@
     <t>粉丝数量</t>
   </si>
   <si>
-    <t>主页链接</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>主页链接</t>
+    </r>
   </si>
   <si>
     <t>平台备注</t>
@@ -221,6 +261,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -239,6 +286,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -254,6 +308,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -269,6 +330,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1534,7 +1602,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -31,6 +31,7 @@
   <authors>
     <author>pc</author>
     <author>chengwei.yang</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -71,16 +72,47 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="1">
+    <comment ref="R1" authorId="2">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">若同个达人有多个默认地址或未选择默认地址，则默认第一行地址为默认地址
-</t>
+          <t xml:space="preserve">
+每个达人请只填写一行地址，多行地址无效，系统将自动忽略。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="2">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不填则默认为否</t>
         </r>
       </text>
     </comment>
@@ -225,6 +257,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -243,6 +282,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -372,7 +418,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,6 +584,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -94,6 +94,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="U1" authorId="2">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>国内则区域必填</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Z1" authorId="2">
       <text>
         <r>
@@ -303,7 +325,19 @@
     </r>
   </si>
   <si>
-    <t>省/州</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>省/州</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1597,7 +1631,8 @@
     <col min="14" max="14" width="14.4583333333333" customWidth="1"/>
     <col min="15" max="15" width="12.4583333333333" customWidth="1"/>
     <col min="16" max="16" width="11.725" customWidth="1"/>
-    <col min="17" max="18" width="11.9083333333333" customWidth="1"/>
+    <col min="17" max="17" width="11.9083333333333" customWidth="1"/>
+    <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="11.6333333333333" customWidth="1"/>
     <col min="22" max="22" width="22.0916666666667" customWidth="1"/>
     <col min="23" max="23" width="13.5416666666667" customWidth="1"/>
@@ -1663,13 +1698,13 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolPartnerInfoTemplate.xlsx
@@ -116,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="2">
+    <comment ref="AA1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="1">
+    <comment ref="AB1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <r>
       <rPr>
@@ -326,6 +326,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -431,6 +438,9 @@
   </si>
   <si>
     <t>联系人邮编</t>
+  </si>
+  <si>
+    <t>收件人税号</t>
   </si>
   <si>
     <t>默认地址</t>
@@ -452,7 +462,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +476,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -949,137 +965,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1087,6 +1103,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1614,7 +1633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.275" customWidth="1"/>
@@ -1637,13 +1656,13 @@
     <col min="22" max="22" width="22.0916666666667" customWidth="1"/>
     <col min="23" max="23" width="13.5416666666667" customWidth="1"/>
     <col min="24" max="24" width="15.8166666666667" customWidth="1"/>
-    <col min="25" max="25" width="10.725" customWidth="1"/>
-    <col min="26" max="26" width="13.0916666666667" customWidth="1"/>
-    <col min="27" max="27" width="14.3666666666667" customWidth="1"/>
-    <col min="28" max="28" width="18.5416666666667" customWidth="1"/>
+    <col min="25" max="26" width="10.725" customWidth="1"/>
+    <col min="27" max="27" width="13.0916666666667" customWidth="1"/>
+    <col min="28" max="28" width="14.3666666666667" customWidth="1"/>
+    <col min="29" max="29" width="18.5416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1738,7 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -1727,14 +1746,17 @@
       </c>
       <c r="AB1" t="s">
         <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>"启用,禁用"</formula1>
     </dataValidation>
   </dataValidations>
